--- a/public/file/Trax Book Corporate Distribution Shipment Template.xlsx
+++ b/public/file/Trax Book Corporate Distribution Shipment Template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maaz Khan\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2401C721-DF57-4479-B7D2-02133AB96CC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33A1A1EA-F195-4226-8910-FEC2BEFD67F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -550,7 +550,7 @@
     <col min="7" max="8" width="36.5546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="21.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="25.6640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="24" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="24.21875" bestFit="1" customWidth="1"/>
